--- a/SOL M6 Scotland.xlsx
+++ b/SOL M6 Scotland.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QA\Scotland\2025 Scotland Level 8 courses\Mod-6 Testing New\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B422BD3D-49A5-44E2-851B-C47D6D4D0CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908FAA5B-92C0-4269-864C-3EED0C148A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -71,49 +71,58 @@
     <t>recap of Day 1</t>
   </si>
   <si>
-    <t>3-Stubs.pptx</t>
-  </si>
-  <si>
-    <t>3-Stubs C# or Java.docx</t>
-  </si>
-  <si>
     <t>2-Unit testing Java or C#.docx</t>
   </si>
   <si>
     <t>1-Testing and SDLC C# or Java.docx</t>
   </si>
   <si>
-    <t>4-Mocks.pptx</t>
-  </si>
-  <si>
-    <t>4-Mocks C# and Java.docx</t>
-  </si>
-  <si>
     <t>5-Selenium.pptx</t>
   </si>
   <si>
     <t>5- Selenium IDE.docx</t>
   </si>
   <si>
-    <t>5-Selnium test - C#.docx</t>
-  </si>
-  <si>
     <t>End of Day 2</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Allow 135m for lab+break</t>
-  </si>
-  <si>
-    <t>Allow 105m for lab+break</t>
-  </si>
-  <si>
     <t>Lecture</t>
   </si>
   <si>
     <t>We no longer teach the IDE</t>
+  </si>
+  <si>
+    <t>5-Selnium test - C#  and Java</t>
+  </si>
+  <si>
+    <t>Code coverage</t>
+  </si>
+  <si>
+    <t>Code coverage lecture</t>
+  </si>
+  <si>
+    <t>3-Code coverage.pptx</t>
+  </si>
+  <si>
+    <t>Lecture Stub</t>
+  </si>
+  <si>
+    <t>4-Stubs.pptx</t>
+  </si>
+  <si>
+    <t>4-Stubs C# or Java.docx</t>
+  </si>
+  <si>
+    <t>Lab + Break</t>
+  </si>
+  <si>
+    <t>5-Mocks.pptx</t>
+  </si>
+  <si>
+    <t>5-Mocks C# and Java.docx</t>
   </si>
 </sst>
 </file>
@@ -140,7 +149,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -171,6 +180,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -184,14 +199,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -203,6 +217,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
@@ -493,24 +513,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="1">
@@ -524,7 +544,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -532,19 +552,19 @@
         <v>0.41666666666666663</v>
       </c>
       <c r="C3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
       <c r="B4" s="1">
-        <f>B3+ TIME(0, C3, 0)</f>
-        <v>0.44791666666666663</v>
+        <f t="shared" ref="B4:B13" si="0">B3+ TIME(0, C3, 0)</f>
+        <v>0.44444444444444442</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -554,78 +574,78 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" ref="B5:B23" si="0">B4+ TIME(0, C4, 0)</f>
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="C5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="C5" s="6">
         <v>45</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>0.48958333333333331</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="C6">
-        <v>60</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
-        <v>1</v>
-      </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.53125</v>
+        <v>0.51041666666666663</v>
       </c>
       <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
+        <v>60</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>1</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>0.5625</v>
-      </c>
-      <c r="C8" s="7">
-        <v>120</v>
-      </c>
-      <c r="D8" s="7" t="s">
+        <v>0.55208333333333326</v>
+      </c>
+      <c r="C8" s="6">
+        <v>90</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>1</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>0.64583333333333337</v>
+        <v>0.61458333333333326</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -633,238 +653,258 @@
       <c r="D9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>1</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.62499999999999989</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>1</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>0.6875</v>
+        <v>0.63541666666666652</v>
       </c>
       <c r="C11">
+        <v>35</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>0.6597222222222221</v>
+      </c>
+      <c r="C12">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>0.68749999999999989</v>
+      </c>
+      <c r="C13">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>2</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B15" s="1">
         <v>0.39583333333333331</v>
-      </c>
-      <c r="C13">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>2</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>0.40625</v>
-      </c>
-      <c r="C14" s="7">
-        <v>90</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>2</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.46875</v>
       </c>
       <c r="C15">
         <v>15</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>2</v>
+      </c>
+      <c r="B16" s="1">
+        <f>B15+ TIME(0, C15, 0)</f>
+        <v>0.40625</v>
+      </c>
+      <c r="C16" s="6">
+        <v>95</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>2</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" ref="B17:B24" si="1">B16+ TIME(0, C16, 0)</f>
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="C17">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="1">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="C18">
+        <v>60</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>2</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="1"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C19" s="6">
+        <v>60</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>2</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="1"/>
+        <v>0.58333333333333326</v>
+      </c>
+      <c r="C20">
+        <v>45</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>2</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="1"/>
+        <v>0.61458333333333326</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+    </row>
+    <row r="22" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11">
         <v>2</v>
       </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C16">
+      <c r="B22" s="1">
+        <f t="shared" si="1"/>
+        <v>0.62499999999999989</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>2</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="1"/>
+        <v>0.62499999999999989</v>
+      </c>
+      <c r="C23">
         <v>60</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="D23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="C17">
-        <v>35</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B24" s="1">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666652</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>2</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>0.54513888888888895</v>
-      </c>
-      <c r="C18" s="7">
-        <v>60</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>2</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>0.58680555555555558</v>
-      </c>
-      <c r="C19">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>2</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>0.61458333333333337</v>
-      </c>
-      <c r="C20">
-        <v>15</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>2</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>0.625</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>2</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>0.625</v>
-      </c>
-      <c r="C22">
-        <v>60</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>2</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SOL M6 Scotland.xlsx
+++ b/SOL M6 Scotland.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QA\Scotland\2025 Scotland Level 8 courses\Mod-6 Testing New\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\QA\2026 QA courses\Scotland\2025 Scotland Level 8 courses\Mod-6 Testing Mike\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908FAA5B-92C0-4269-864C-3EED0C148A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F965E38A-A385-4896-936C-8C0DC957AA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -44,9 +44,6 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>Slide</t>
-  </si>
-  <si>
     <t>Lab</t>
   </si>
   <si>
@@ -71,18 +68,9 @@
     <t>recap of Day 1</t>
   </si>
   <si>
-    <t>2-Unit testing Java or C#.docx</t>
-  </si>
-  <si>
     <t>1-Testing and SDLC C# or Java.docx</t>
   </si>
   <si>
-    <t>5-Selenium.pptx</t>
-  </si>
-  <si>
-    <t>5- Selenium IDE.docx</t>
-  </si>
-  <si>
     <t>End of Day 2</t>
   </si>
   <si>
@@ -95,34 +83,477 @@
     <t>We no longer teach the IDE</t>
   </si>
   <si>
-    <t>5-Selnium test - C#  and Java</t>
-  </si>
-  <si>
-    <t>Code coverage</t>
-  </si>
-  <si>
-    <t>Code coverage lecture</t>
-  </si>
-  <si>
-    <t>3-Code coverage.pptx</t>
-  </si>
-  <si>
-    <t>Lecture Stub</t>
-  </si>
-  <si>
-    <t>4-Stubs.pptx</t>
-  </si>
-  <si>
-    <t>4-Stubs C# or Java.docx</t>
-  </si>
-  <si>
     <t>Lab + Break</t>
   </si>
   <si>
     <t>5-Mocks.pptx</t>
   </si>
   <si>
-    <t>5-Mocks C# and Java.docx</t>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>EG 06 - Test-driven development.docx</t>
+  </si>
+  <si>
+    <t>EG 02-Unit testing Java or C#.docx</t>
+  </si>
+  <si>
+    <t>EG 03-Code coverage.pptx</t>
+  </si>
+  <si>
+    <t>EG 03- Code coverage.docx</t>
+  </si>
+  <si>
+    <t>EG 04-Stubs.pptx</t>
+  </si>
+  <si>
+    <t>EG 04-Stubs C# or Java.docx</t>
+  </si>
+  <si>
+    <t>EG 05-Mocks C# and Java.docx</t>
+  </si>
+  <si>
+    <t>Selenium IDE.docx</t>
+  </si>
+  <si>
+    <t>7-Selenium.pptx</t>
+  </si>
+  <si>
+    <t>6-Test-driven development.pptx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecture </t>
+  </si>
+  <si>
+    <t>EG 07-Selnium test - C#.docx                 EG 07-Selnium test - Java.docx</t>
+  </si>
+  <si>
+    <t>Ks</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Analysing requirements to determine appropriate testing strategies</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Designing and implementing test plans with instrumented code </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Computing test coverage and yield according to specified criteria to ensure test cases are covering all functionality of the software </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Identifying how much code is exercised when test cases are run </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Writing tests in various contexts (including unit testing, system testing, integration testing and load testing) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Applying industry standard testing techniques </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Producing suitable test data to cover the range of possible and impossible inputs, each designed to prove software works or to highlight any flaws </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Performing usability testing to ensure that software will operate correctly under live user situations </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Identifying, tracking, and fixing bugs identified in software, recreating the bug, and escalating if necessary </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Supporting software quality assurance and acceptance testing of the final solution </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Contributing to test reports and communicate test results</t>
+    </r>
+  </si>
+  <si>
+    <t>From Unit SDS019 – Developing Software</t>
+  </si>
+  <si>
+    <t>P9 - Using third party integration tools (screen scraping data and integrating to other systems) to capture, reformat and display data more conveniently </t>
+  </si>
+  <si>
+    <t>Ps</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The purpose of testing and ensuring new and amended systems, configurations, packages, or services, together with any interfaces, perform as specified </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The testing life cycle and how it is applied to software development projects </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The role of testing within software development, as a tool for design improvement as well as a validation process</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>What is meant by Test Driven Development (TDD) and the test pyramid </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>How development is underpinned by testing </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>How to select and apply a testing strategy and testing techniques that are appropriate to a particular software system or component </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>How to create a test plan </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>How to design test cases and create test scripts and test data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The different test techniques for performing unit testing, system testing integration testing and load testing </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>10.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The importance of identifying opportunities for automated testing and implementing these </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The role of usability testing and how to implement this </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>12.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The importance of representative and accurate test data and data volumes as well as deliberately wrong data to support software testing </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>13.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The use of bug tracking tools to record and manage resolution</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>14.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The difference between bugs and enhancements, and the need to agree to replan software development to accommodate these </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>15.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>The relevant legislation and internal/external standards related to software testing and how to apply these </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>16.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>How to assess test results against expected results and acceptance criteria and verify these through traceability to software requirements</t>
+    </r>
+  </si>
+  <si>
+    <t>K10 - How to implement unit testing at each stage of software development</t>
+  </si>
+  <si>
+    <t>Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-day highly practical workshop which will discuss the following topics: </t>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF004050"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Writing unit tests for developed test plans and cases (with data) in a TDD format</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF004050"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Using tracking tools to monitor and work on bugs and enhancements</t>
+    </r>
+  </si>
+  <si>
+    <t>This content will be written with the Ks and Ps of the unit in mind. Learners should work through a project simulation from concept to close, creating project assets at each stage to enable them to complete the apply requirements back in the workplace.</t>
+  </si>
+  <si>
+    <t>Covers Integration testing</t>
+  </si>
+  <si>
+    <r>
+      <t>•</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF004050"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t>Write different test types for an application, such as unit tests, integration tests, and load tests</t>
+    </r>
+  </si>
+  <si>
+    <t>The slides and labs do not cover Load testing</t>
   </si>
 </sst>
 </file>
@@ -132,7 +563,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,8 +579,92 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="+mj-lt"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="+mj-lt"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="+mj-lt"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF004050"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF004050"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +701,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -199,10 +720,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -222,7 +742,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,408 +1059,713 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q71"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" customWidth="1"/>
     <col min="4" max="4" width="26.5546875" customWidth="1"/>
-    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="D1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>0.39583333333333331</v>
       </c>
       <c r="C2">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <f>B2+ TIME(0, C2, 0)</f>
-        <v>0.41666666666666663</v>
+        <v>0.40972222222222221</v>
       </c>
       <c r="C3">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7">
         <v>1</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B13" si="0">B3+ TIME(0, C3, 0)</f>
-        <v>0.44444444444444442</v>
+        <v>0.43055555555555552</v>
       </c>
       <c r="C4">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="D4" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>0.4548611111111111</v>
-      </c>
-      <c r="C5" s="6">
-        <v>45</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>3</v>
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="C5" s="5">
+        <v>40</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7">
         <v>1</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>0.4861111111111111</v>
+        <v>0.46875</v>
       </c>
       <c r="C6">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>0.51041666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
         <v>60</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="D7" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7">
         <v>1</v>
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>0.55208333333333326</v>
-      </c>
-      <c r="C8" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="C8" s="5">
         <v>90</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>3</v>
+      <c r="D8" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7">
         <v>1</v>
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>0.61458333333333326</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C9">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="D9" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7">
         <v>1</v>
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>0.62499999999999989</v>
+        <v>0.61458333333333326</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7">
         <v>1</v>
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>0.63541666666666652</v>
+        <v>0.62499999999999989</v>
       </c>
       <c r="C11">
-        <v>35</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7">
         <v>1</v>
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>0.6597222222222221</v>
+        <v>0.65277777777777768</v>
       </c>
       <c r="C12">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="17">
         <v>1</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="15">
         <f t="shared" si="0"/>
-        <v>0.68749999999999989</v>
-      </c>
-      <c r="C13">
+        <v>0.68402777777777768</v>
+      </c>
+      <c r="C13" s="2">
         <v>0</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="D13" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7">
         <v>2</v>
       </c>
       <c r="B15" s="1">
         <v>0.39583333333333331</v>
       </c>
       <c r="C15">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="D15" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7">
         <v>2</v>
       </c>
       <c r="B16" s="1">
         <f>B15+ TIME(0, C15, 0)</f>
-        <v>0.40625</v>
-      </c>
-      <c r="C16" s="6">
-        <v>95</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
+        <v>0.40277777777777773</v>
+      </c>
+      <c r="C16" s="5">
+        <v>75</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="17" spans="1:6">
+      <c r="A17" s="7">
         <v>2</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" ref="B17:B24" si="1">B16+ TIME(0, C16, 0)</f>
-        <v>0.47222222222222221</v>
+        <f t="shared" ref="B17:B26" si="1">B16+ TIME(0, C16, 0)</f>
+        <v>0.45486111111111105</v>
       </c>
       <c r="C17">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7"/>
       <c r="B18" s="1">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.47569444444444436</v>
       </c>
       <c r="C18">
         <v>60</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="D18" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="7">
         <v>2</v>
       </c>
       <c r="B19" s="1">
         <f t="shared" si="1"/>
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="C19" s="6">
+        <v>0.51736111111111105</v>
+      </c>
+      <c r="C19" s="5">
         <v>60</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>3</v>
+      <c r="D19" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="7">
         <v>2</v>
       </c>
       <c r="B20" s="1">
         <f t="shared" si="1"/>
-        <v>0.58333333333333326</v>
-      </c>
-      <c r="C20">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
+        <v>0.55902777777777768</v>
+      </c>
+      <c r="C20" s="5">
+        <v>20</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7">
         <v>2</v>
       </c>
       <c r="B21" s="1">
         <f t="shared" si="1"/>
-        <v>0.61458333333333326</v>
-      </c>
-      <c r="C21">
-        <v>15</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+        <v>0.57291666666666652</v>
+      </c>
+      <c r="C21" s="5">
+        <v>60</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="7">
         <v>2</v>
       </c>
       <c r="B22" s="1">
         <f t="shared" si="1"/>
-        <v>0.62499999999999989</v>
-      </c>
-      <c r="C22" s="12">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+        <v>0.61458333333333315</v>
+      </c>
+      <c r="C22">
+        <v>30</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="7">
         <v>2</v>
       </c>
       <c r="B23" s="1">
         <f t="shared" si="1"/>
-        <v>0.62499999999999989</v>
+        <v>0.63541666666666652</v>
       </c>
       <c r="C23">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="11" customFormat="1">
+      <c r="A24" s="10">
         <v>2</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="1"/>
-        <v>0.66666666666666652</v>
-      </c>
-      <c r="C24">
+        <v>0.64583333333333315</v>
+      </c>
+      <c r="C24" s="11">
         <v>0</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="D24" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.8">
+      <c r="A25" s="7">
+        <v>2</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="1"/>
+        <v>0.64583333333333315</v>
+      </c>
+      <c r="C25">
+        <v>60</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="17">
+        <v>2</v>
+      </c>
+      <c r="B26" s="15">
+        <f t="shared" si="1"/>
+        <v>0.68749999999999978</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="29" spans="1:6" ht="23.4">
+      <c r="A29" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16.2">
+      <c r="A30" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="16.2">
+      <c r="A31" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="16.2">
+      <c r="A32" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="16.2">
+      <c r="A33" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="16.2">
+      <c r="A34" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="16.2">
+      <c r="A35" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="16.2">
+      <c r="A36" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="16.2">
+      <c r="A37" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:17" ht="16.2">
+      <c r="A38" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="16.2">
+      <c r="A39" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="16.2">
+      <c r="A40" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15">
+      <c r="A41" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+    </row>
+    <row r="42" spans="1:17" ht="16.2">
+      <c r="A42" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+    </row>
+    <row r="44" spans="1:17" ht="21">
+      <c r="A44" s="24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15">
+      <c r="A61" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+    </row>
+    <row r="62" spans="1:9" ht="15">
+      <c r="A62" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+    </row>
+    <row r="64" spans="1:9" ht="21">
+      <c r="A64" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.2">
+      <c r="A65" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.2">
+      <c r="A66" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="16.2">
+      <c r="A67" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="16.2">
+      <c r="A68" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="16.2">
+      <c r="A69" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="21">
+      <c r="B71" s="29" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
